--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -68268,7 +68268,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6496643518</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>38352</v>
@@ -68289,6 +68289,32 @@
         <v>1086</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.5633449074</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>9658</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -68294,7 +68294,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.5633449074</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>9658</v>
@@ -68315,6 +68315,32 @@
         <v>1051</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.5660300926</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>20500</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>0.234999999403954</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>0.234999999403954</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>0.234999999403954</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>0.234999999403954</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -68320,7 +68320,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.5660300926</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>20500</v>
@@ -68341,6 +68341,32 @@
         <v>1086</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6205324074</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>25310</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>0.24099999666214</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>0.233999997377396</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>0.234999999403954</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>0.233999997377396</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -68346,7 +68346,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6205324074</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>25310</v>
@@ -68367,6 +68367,32 @@
         <v>1082</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.649375</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>20142</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>0.234999999403954</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>0.233999997377396</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -68372,7 +68372,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.649375</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>20142</v>
@@ -68381,7 +68381,7 @@
         <v>0.239999994635582</v>
       </c>
       <c r="D2491" t="n">
-        <v>0.234999999403954</v>
+        <v>0.233999997377396</v>
       </c>
       <c r="E2491" t="n">
         <v>0.239999994635582</v>
@@ -68393,6 +68393,32 @@
         <v>1082</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6242824074</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>92185</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>0.233999997377396</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>0.233999997377396</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -68398,7 +68398,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6242824074</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>92185</v>
@@ -68419,6 +68419,32 @@
         <v>1049</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.5644328704</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>63684</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -68424,13 +68424,13 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.5644328704</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
-        <v>63684</v>
+        <v>0</v>
       </c>
       <c r="C2493" t="n">
-        <v>0.238000005483627</v>
+        <v>0.232999995350838</v>
       </c>
       <c r="D2493" t="n">
         <v>0.232999995350838</v>

--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -68448,6 +68448,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.2916666667</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>89803</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -68474,6 +68474,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.2916666667</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>101085</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>0.224999994039536</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="1094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="1095">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -3294,6 +3294,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.239999994635582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.228000000119209</t>
   </si>
 </sst>
 </file>
@@ -68500,6 +68503,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.2916666667</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>65257</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>0.222000002861023</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>0.223000004887581</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="1096">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -3297,6 +3297,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.228000000119209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.222000002861023</t>
   </si>
 </sst>
 </file>
@@ -68529,6 +68532,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.2916666667</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>120350</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>0.222000002861023</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>0.232999995350838</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>0.222000002861023</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GG.MI.xlsx
+++ b/data/GG.MI.xlsx
@@ -68558,6 +68558,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.3333333333</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>67768</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>0.221000000834465</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>0.224000006914139</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>0.222000002861023</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
